--- a/src/src/main/webapp/portal/woMgr/mvs/APM_MVSWorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/woMgr/mvs/APM_MVSWorkOrder_Template.xlsx
@@ -44,7 +44,7 @@
     <t>数量</t>
   </si>
   <si>
-    <t>单价</t>
+    <t>采购单价</t>
   </si>
   <si>
     <t>序列号</t>
@@ -1503,24 +1503,23 @@
   <dimension ref="A1:IS10"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.4922" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.3516" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1719" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1719" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.0938" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.8125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.2188" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.2422" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.4453" style="1" customWidth="1"/>
+    <col min="5" max="6" width="11.1719" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8516" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1719" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.3516" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="1" customWidth="1"/>
     <col min="11" max="12" width="8.85156" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.25" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7031" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8047" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.2031" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.3359" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.6016" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.2656" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.3516" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6719" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8516" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1719" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.3516" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.6719" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16.3516" style="1" customWidth="1"/>
     <col min="20" max="253" width="8.85156" style="1" customWidth="1"/>
     <col min="254" max="256" width="8.85156" style="1" customWidth="1"/>
   </cols>
@@ -10016,8 +10015,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/src/src/main/webapp/portal/woMgr/mvs/APM_MVSWorkOrder_Template.xlsx
+++ b/src/src/main/webapp/portal/woMgr/mvs/APM_MVSWorkOrder_Template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>报修时间</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>发票号</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>质保期</t>
@@ -1500,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:IS10"/>
+  <dimension ref="A1:IT10"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -1514,14 +1517,14 @@
     <col min="10" max="10" width="11.5" style="1" customWidth="1"/>
     <col min="11" max="12" width="8.85156" style="1" customWidth="1"/>
     <col min="13" max="13" width="12.3516" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.6719" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.8516" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1719" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.3516" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.6719" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.3516" style="1" customWidth="1"/>
-    <col min="20" max="253" width="8.85156" style="1" customWidth="1"/>
-    <col min="254" max="256" width="8.85156" style="1" customWidth="1"/>
+    <col min="14" max="15" width="14.6719" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.8516" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.1719" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.3516" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.6719" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.3516" style="1" customWidth="1"/>
+    <col min="21" max="254" width="8.85156" style="1" customWidth="1"/>
+    <col min="255" max="256" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -1582,8 +1585,10 @@
       <c r="S1" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="T1" s="3"/>
-      <c r="U1" s="4"/>
+      <c r="T1" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3"/>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
@@ -1815,7 +1820,8 @@
       <c r="IP1" s="4"/>
       <c r="IQ1" s="4"/>
       <c r="IR1" s="4"/>
-      <c r="IS1" s="5"/>
+      <c r="IS1" s="4"/>
+      <c r="IT1" s="5"/>
     </row>
     <row r="2" ht="13.65" customHeight="1">
       <c r="A2" s="3"/>
@@ -1837,7 +1843,7 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
-      <c r="T2" s="6"/>
+      <c r="T2" s="4"/>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
@@ -2070,7 +2076,8 @@
       <c r="IP2" s="6"/>
       <c r="IQ2" s="6"/>
       <c r="IR2" s="6"/>
-      <c r="IS2" s="7"/>
+      <c r="IS2" s="6"/>
+      <c r="IT2" s="7"/>
     </row>
     <row r="3" ht="13.65" customHeight="1">
       <c r="A3" s="8"/>
@@ -2325,7 +2332,8 @@
       <c r="IP3" s="6"/>
       <c r="IQ3" s="6"/>
       <c r="IR3" s="6"/>
-      <c r="IS3" s="7"/>
+      <c r="IS3" s="6"/>
+      <c r="IT3" s="7"/>
     </row>
     <row r="4" ht="13.65" customHeight="1">
       <c r="A4" s="8"/>
@@ -2580,7 +2588,8 @@
       <c r="IP4" s="6"/>
       <c r="IQ4" s="6"/>
       <c r="IR4" s="6"/>
-      <c r="IS4" s="7"/>
+      <c r="IS4" s="6"/>
+      <c r="IT4" s="7"/>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" s="8"/>
@@ -2835,7 +2844,8 @@
       <c r="IP5" s="6"/>
       <c r="IQ5" s="6"/>
       <c r="IR5" s="6"/>
-      <c r="IS5" s="7"/>
+      <c r="IS5" s="6"/>
+      <c r="IT5" s="7"/>
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" s="8"/>
@@ -3090,7 +3100,8 @@
       <c r="IP6" s="6"/>
       <c r="IQ6" s="6"/>
       <c r="IR6" s="6"/>
-      <c r="IS6" s="7"/>
+      <c r="IS6" s="6"/>
+      <c r="IT6" s="7"/>
     </row>
     <row r="7" ht="13.65" customHeight="1">
       <c r="A7" s="8"/>
@@ -3345,7 +3356,8 @@
       <c r="IP7" s="6"/>
       <c r="IQ7" s="6"/>
       <c r="IR7" s="6"/>
-      <c r="IS7" s="7"/>
+      <c r="IS7" s="6"/>
+      <c r="IT7" s="7"/>
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" s="8"/>
@@ -3600,7 +3612,8 @@
       <c r="IP8" s="6"/>
       <c r="IQ8" s="6"/>
       <c r="IR8" s="6"/>
-      <c r="IS8" s="7"/>
+      <c r="IS8" s="6"/>
+      <c r="IT8" s="7"/>
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" s="8"/>
@@ -3855,7 +3868,8 @@
       <c r="IP9" s="6"/>
       <c r="IQ9" s="6"/>
       <c r="IR9" s="6"/>
-      <c r="IS9" s="7"/>
+      <c r="IS9" s="6"/>
+      <c r="IT9" s="7"/>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" s="9"/>
@@ -4110,7 +4124,8 @@
       <c r="IP10" s="10"/>
       <c r="IQ10" s="10"/>
       <c r="IR10" s="10"/>
-      <c r="IS10" s="11"/>
+      <c r="IS10" s="10"/>
+      <c r="IT10" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4133,7 +4148,7 @@
   <sheetData>
     <row r="1" ht="13.7" customHeight="1">
       <c r="A1" t="s" s="13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4643,7 +4658,7 @@
     </row>
     <row r="3" ht="15.95" customHeight="1">
       <c r="A3" t="s" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="6"/>
@@ -4899,7 +4914,7 @@
     </row>
     <row r="4" ht="15.95" customHeight="1">
       <c r="A4" t="s" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="6"/>
@@ -5155,7 +5170,7 @@
     </row>
     <row r="5" ht="15.95" customHeight="1">
       <c r="A5" t="s" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="6"/>
@@ -5411,7 +5426,7 @@
     </row>
     <row r="6" ht="15.95" customHeight="1">
       <c r="A6" t="s" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="6"/>
@@ -5667,7 +5682,7 @@
     </row>
     <row r="7" ht="15.95" customHeight="1">
       <c r="A7" t="s" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="6"/>
@@ -5923,7 +5938,7 @@
     </row>
     <row r="8" ht="15.95" customHeight="1">
       <c r="A8" t="s" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="6"/>
@@ -6179,7 +6194,7 @@
     </row>
     <row r="9" ht="15.95" customHeight="1">
       <c r="A9" t="s" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="6"/>
@@ -6435,7 +6450,7 @@
     </row>
     <row r="10" ht="15.95" customHeight="1">
       <c r="A10" t="s" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="6"/>
@@ -6945,7 +6960,7 @@
     </row>
     <row r="12" ht="13.7" customHeight="1">
       <c r="A12" t="s" s="18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7455,7 +7470,7 @@
     </row>
     <row r="14" ht="15.95" customHeight="1">
       <c r="A14" t="s" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="6"/>
@@ -7711,7 +7726,7 @@
     </row>
     <row r="15" ht="15.95" customHeight="1">
       <c r="A15" t="s" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="6"/>
@@ -7967,7 +7982,7 @@
     </row>
     <row r="16" ht="15.95" customHeight="1">
       <c r="A16" t="s" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="6"/>
@@ -8223,7 +8238,7 @@
     </row>
     <row r="17" ht="15.95" customHeight="1">
       <c r="A17" t="s" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="6"/>
@@ -8479,7 +8494,7 @@
     </row>
     <row r="18" ht="15.95" customHeight="1">
       <c r="A18" t="s" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="6"/>
@@ -8735,7 +8750,7 @@
     </row>
     <row r="19" ht="15.95" customHeight="1">
       <c r="A19" t="s" s="15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="6"/>
@@ -8991,7 +9006,7 @@
     </row>
     <row r="20" ht="15.95" customHeight="1">
       <c r="A20" t="s" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="6"/>
@@ -9247,7 +9262,7 @@
     </row>
     <row r="21" ht="15.95" customHeight="1">
       <c r="A21" t="s" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="6"/>
@@ -9503,7 +9518,7 @@
     </row>
     <row r="22" ht="15.95" customHeight="1">
       <c r="A22" t="s" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="6"/>
@@ -9759,7 +9774,7 @@
     </row>
     <row r="23" ht="13.5" customHeight="1">
       <c r="A23" t="s" s="15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="10"/>
@@ -10015,8 +10030,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
